--- a/file/tracking-jibang.xlsx
+++ b/file/tracking-jibang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D0837-1610-4CCD-B7A7-C51DD48EF9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D2835-3714-4CB5-9485-B10C71563BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A9EBCE60-27B1-4083-8D39-6BB6095E1657}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A9EBCE60-27B1-4083-8D39-6BB6095E1657}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>크로바</t>
   </si>
@@ -328,13 +328,49 @@
   </si>
   <si>
     <t>서면비스타동원</t>
+  </si>
+  <si>
+    <t>삼산타운7단지주공</t>
+  </si>
+  <si>
+    <t>삼산타운6단지주공</t>
+  </si>
+  <si>
+    <t>브라운스톤부평</t>
+  </si>
+  <si>
+    <t>부평SKVIEW해모로</t>
+  </si>
+  <si>
+    <t>부개역푸르지오</t>
+  </si>
+  <si>
+    <t>래미안부평</t>
+  </si>
+  <si>
+    <t>동아2단지</t>
+  </si>
+  <si>
+    <t>부평캐슬&amp;더샵퍼스트</t>
+  </si>
+  <si>
+    <t>e편한세상부평그랑힐스</t>
+  </si>
+  <si>
+    <t>더샵부평센트럴시티</t>
+  </si>
+  <si>
+    <t>힐스테이트부평</t>
+  </si>
+  <si>
+    <t>산곡푸르지오</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +388,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -406,7 +448,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -436,6 +478,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -752,7 +803,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936DD677-8B58-4B8E-9FA7-9F253B63BAAD}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
@@ -1550,6 +1601,102 @@
         <v>99</v>
       </c>
     </row>
+    <row r="100" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
+        <v>10415</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
+        <v>10414</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="11">
+        <v>133678</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
+        <v>132386</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="11">
+        <v>26825</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>104629</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>2331</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
+        <v>140025</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10">
+        <v>139343</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="10">
+        <v>147824</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="10">
+        <v>129967</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="10">
+        <v>100515</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
